--- a/reports/business-plan/financial_model.xlsx
+++ b/reports/business-plan/financial_model.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -530,60 +530,60 @@
         <v>60000</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>156000</v>
+        <v>175000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>600000</v>
+        <v>455000</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1360000</v>
+        <v>877500</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2160000</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>School Standard ($6-8 / student / yr)</t>
+          <t>School Standard ($6-7 / student / yr)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>105000</v>
+        <v>75000</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>227500</v>
+        <v>201500</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>525000</v>
+        <v>439400</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>914250</v>
+        <v>759780</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1540000</v>
+        <v>1197840</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>School Premium ($10-14 / student / yr)</t>
+          <t>School Premium ($10-12 / student / yr)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>90000</v>
+        <v>60000</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>264000</v>
+        <v>189000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>576000</v>
+        <v>443300</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1047800</v>
+        <v>796950</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1820000</v>
+        <v>1303900</v>
       </c>
     </row>
     <row r="8">
@@ -599,406 +599,318 @@
         <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>247500</v>
+        <v>198000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>603750</v>
+        <v>498750</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1200000</v>
+        <v>1062000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Parent Premium ($72-80 / yr)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>216000</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>418000</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>640000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>After-School Programs ($300-400 / mo / program)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>540000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1176000</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1920000</v>
-      </c>
-    </row>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>195000</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>565500</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1535700</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2932980</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>4963740</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OEM / API partners ($120K avg)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>220000</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>480000</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>COSTS</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Custom development + data licensing</t>
+          <t>Engineering &amp; R&amp;D</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>200000</v>
+        <v>1200000</v>
       </c>
       <c r="F12" s="4" t="n">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Game Design &amp; Content</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>500000</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>255000</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>742500</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>2704500</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>5939800</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10260000</v>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="F14" s="4" t="n">
+        <v>800000</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>COSTS</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>180000</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1900000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineering &amp; R&amp;D</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>220000</v>
+        <v>30000</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>450000</v>
+        <v>100000</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>900000</v>
+        <v>200000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1500000</v>
+        <v>400000</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2100000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Game Design &amp; Content</t>
+          <t>Research &amp; Curriculum</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>80000</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>200000</v>
-      </c>
       <c r="D17" s="4" t="n">
-        <v>450000</v>
+        <v>130000</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>800000</v>
+        <v>180000</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1100000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure</t>
+          <t>G&amp;A (legal, finance, ops)</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
         <v>60000</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="E18" s="4" t="n">
+        <v>380000</v>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>600000</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>1000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing</t>
+          <t>Compliance / data governance</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>150000</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1500000</v>
-      </c>
       <c r="F19" s="4" t="n">
-        <v>2200000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Customer Success</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Research &amp; Curriculum</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>220000</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>300000</v>
-      </c>
-    </row>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total Costs</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>640000</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>4810000</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>6950000</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>G&amp;A (legal, finance, ops)</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>80000</v>
+        <v>-445000</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>150000</v>
+        <v>-914500</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>250000</v>
+        <v>-1244300</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>500000</v>
+        <v>-1877020</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>900000</v>
+        <v>-1986260</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Compliance / data governance</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>220000</v>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-228.2%</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-161.7%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-81.0%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-64.0%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-40.0%</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Total Costs</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>720000</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>3120000</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>8620000</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>-465000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>-907500</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-415500</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>139800</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>1640000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Operating margin %</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>-182.4%</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>-122.2%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>-15.4%</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Cumulative cash flow</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>-465000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>-1372500</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>-1788000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>-1648200</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>-8200</v>
+      <c r="B24" s="4" t="n">
+        <v>-445000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-1359500</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-2603800</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>-4480820</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>-6467080</v>
       </c>
     </row>
   </sheetData>
@@ -1450,17 +1362,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.2×</t>
+          <t>0.8×</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.8×</t>
+          <t>0.9×</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GCC pilot conversion stalls; only 50% of base ARR realized; trading at a discount EdTech multiple</t>
+          <t>GCC pilot conversion stalls; only 50% of base ARR realized; trading at distressed-EdTech multiple</t>
         </is>
       </c>
     </row>
@@ -1472,17 +1384,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.8×</t>
+          <t>2.7×</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15.9×</t>
+          <t>3.8×</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BMC plan executes; Series A 2028 at industry-median EdTech revenue multiple (10×)</t>
+          <t>Plan executes; Series A 2028 at current EdTech median revenue multiple (~5× public comp; ~6-8× private growth)</t>
         </is>
       </c>
     </row>
@@ -1494,17 +1406,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18.2×</t>
+          <t>6.4×</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>30.5×</t>
+          <t>10.5×</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GCC ministries adopt + GCC private chain partnership; Kahoot-style 11-12× multiple</t>
+          <t>GCC ministries adopt + US Clever partnership lands; private growth multiple (8× ARR per Q4 2025 Finrofca private-comp range)</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1435,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$2,704,500</t>
+          <t>$1,535,700</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1447,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$5,939,800</t>
+          <t>$2,932,980</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1459,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$59,398,000</t>
+          <t>$14,664,900</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1483,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$5,411,818</t>
+          <t>$1,336,135</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1495,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.8×</t>
+          <t>2.7×</t>
         </is>
       </c>
     </row>
@@ -1633,22 +1545,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineering hires (3 new + AI tooling)</t>
+          <t>GTM: 2 BD hires + founder travel + GESS/BETT</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Go-to-market: 1 founder-led BD + GESS/BETT</t>
+          <t>Engineering (1 senior hire + AI tooling)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -1663,22 +1575,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pilots + content (3 game updates + curriculum mapping)</t>
+          <t>Pilots + content + 1 wedge-game deepening</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compliance + legal (KSA PDPL, COPPA, contracts)</t>
+          <t>Compliance + legal (KSA PDPL, COPPA, SAFE)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -1697,11 +1609,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
